--- a/STEGO-K1 판매 프로세스 A to Z.xlsx
+++ b/STEGO-K1 판매 프로세스 A to Z.xlsx
@@ -1,29 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\문서\1. 이브이앤솔루션\20. AI\2. 목표관리시스템\evn-warp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D01EE8-6BE6-4343-8A1C-E3166C925882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF0039E-ADA4-441E-83F1-7AAED3073710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{9F6BE4B8-81B1-465B-9F37-12E790C0CAE2}"/>
+    <workbookView xWindow="-28920" yWindow="4095" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{9F6BE4B8-81B1-465B-9F37-12E790C0CAE2}"/>
   </bookViews>
   <sheets>
     <sheet name="프로세스" sheetId="5" r:id="rId1"/>
     <sheet name="판매 프로세스 양식" sheetId="2" r:id="rId2"/>
-    <sheet name="1.전진영" sheetId="3" r:id="rId3"/>
-    <sheet name="2.이브이앤솔루션" sheetId="4" r:id="rId4"/>
+    <sheet name="영업퍼널 전환비율" sheetId="6" r:id="rId3"/>
+    <sheet name="1.전진영" sheetId="3" r:id="rId4"/>
+    <sheet name="2.이브이앤솔루션" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'1.전진영'!$B$4:$I$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2.이브이앤솔루션'!$B$4:$I$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'1.전진영'!$B$4:$I$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2.이브이앤솔루션'!$B$4:$I$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'판매 프로세스 양식'!$B$4:$I$48</definedName>
   </definedNames>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="242">
   <si>
     <t>고객명</t>
   </si>
@@ -1897,15 +1898,36 @@
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>단계</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>리드 단계</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>판매목표</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전환율(%)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>필요 리드 수량</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2048,6 +2070,14 @@
       <name val="Segoe UI"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="13">
@@ -2200,12 +2230,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2292,23 +2328,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2316,7 +2352,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
@@ -2331,20 +2370,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="백분율" xfId="2" builtinId="5"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2704,10 +2739,10 @@
       </c>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="27" t="s">
         <v>183</v>
       </c>
       <c r="D3" s="25" t="s">
@@ -2719,19 +2754,19 @@
       <c r="F3" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="I3" s="40" t="s">
+      <c r="I3" s="29" t="s">
         <v>221</v>
       </c>
-      <c r="J3" s="40" t="s">
+      <c r="J3" s="29" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="27"/>
-      <c r="C4" s="29" t="s">
+      <c r="B4" s="36"/>
+      <c r="C4" s="35" t="s">
         <v>184</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="36" t="s">
         <v>171</v>
       </c>
       <c r="E4" s="26" t="s">
@@ -2740,36 +2775,36 @@
       <c r="F4" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="I4" s="41" t="s">
+      <c r="I4" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="J4" s="42" t="s">
+      <c r="J4" s="31" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="5" spans="2:10">
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
       <c r="E5" s="26" t="s">
         <v>174</v>
       </c>
       <c r="F5" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="I5" s="41" t="s">
+      <c r="I5" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="J5" s="43" t="s">
+      <c r="J5" s="32" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="29">
-      <c r="B6" s="27"/>
-      <c r="C6" s="29" t="s">
+      <c r="B6" s="36"/>
+      <c r="C6" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="36" t="s">
         <v>176</v>
       </c>
       <c r="E6" s="26" t="s">
@@ -2778,35 +2813,35 @@
       <c r="F6" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="I6" s="41" t="s">
+      <c r="I6" s="30" t="s">
         <v>228</v>
       </c>
-      <c r="J6" s="43" t="s">
+      <c r="J6" s="32" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="27"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="27"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="36"/>
       <c r="E7" s="26" t="s">
         <v>192</v>
       </c>
       <c r="F7" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="I7" s="41" t="s">
+      <c r="I7" s="30" t="s">
         <v>229</v>
       </c>
-      <c r="J7" s="43" t="s">
+      <c r="J7" s="32" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="36" t="s">
         <v>191</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="28" t="s">
         <v>186</v>
       </c>
       <c r="D8" s="25" t="s">
@@ -2816,16 +2851,16 @@
         <v>196</v>
       </c>
       <c r="F8" s="26"/>
-      <c r="I8" s="41" t="s">
+      <c r="I8" s="30" t="s">
         <v>230</v>
       </c>
-      <c r="J8" s="42" t="s">
+      <c r="J8" s="31" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="27"/>
-      <c r="C9" s="30" t="s">
+      <c r="B9" s="36"/>
+      <c r="C9" s="28" t="s">
         <v>188</v>
       </c>
       <c r="D9" s="25" t="s">
@@ -2835,16 +2870,16 @@
         <v>197</v>
       </c>
       <c r="F9" s="26"/>
-      <c r="I9" s="41" t="s">
+      <c r="I9" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="J9" s="42" t="s">
+      <c r="J9" s="31" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="10" spans="2:10">
-      <c r="B10" s="27"/>
-      <c r="C10" s="30" t="s">
+      <c r="B10" s="36"/>
+      <c r="C10" s="28" t="s">
         <v>189</v>
       </c>
       <c r="D10" s="25" t="s">
@@ -2854,51 +2889,51 @@
         <v>198</v>
       </c>
       <c r="F10" s="26"/>
-      <c r="I10" s="41" t="s">
+      <c r="I10" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="J10" s="42"/>
+      <c r="J10" s="31"/>
     </row>
     <row r="11" spans="2:10">
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="36" t="s">
         <v>194</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="36" t="s">
         <v>195</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>199</v>
       </c>
       <c r="F11" s="26"/>
-      <c r="I11" s="41" t="s">
+      <c r="I11" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="J11" s="42"/>
+      <c r="J11" s="31"/>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
       <c r="E12" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F12" s="26"/>
     </row>
     <row r="13" spans="2:10">
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
       <c r="E13" s="26" t="s">
         <v>201</v>
       </c>
       <c r="F13" s="26"/>
     </row>
     <row r="14" spans="2:10">
-      <c r="B14" s="27"/>
-      <c r="C14" s="36" t="s">
+      <c r="B14" s="36"/>
+      <c r="C14" s="37" t="s">
         <v>206</v>
       </c>
       <c r="D14" s="33" t="s">
@@ -2910,17 +2945,17 @@
       <c r="F14" s="26"/>
     </row>
     <row r="15" spans="2:10">
-      <c r="B15" s="27"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="39"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="40"/>
       <c r="E15" s="26" t="s">
         <v>203</v>
       </c>
       <c r="F15" s="26"/>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="27"/>
-      <c r="C16" s="38"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="39"/>
       <c r="D16" s="34"/>
       <c r="E16" s="26" t="s">
         <v>204</v>
@@ -2928,8 +2963,8 @@
       <c r="F16" s="26"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="27"/>
-      <c r="C17" s="30" t="s">
+      <c r="B17" s="36"/>
+      <c r="C17" s="28" t="s">
         <v>216</v>
       </c>
       <c r="D17" s="25" t="s">
@@ -2944,7 +2979,7 @@
       <c r="B18" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="28" t="s">
         <v>211</v>
       </c>
       <c r="D18" s="25" t="s">
@@ -2957,24 +2992,19 @@
     </row>
     <row r="19" spans="2:6">
       <c r="B19" s="34"/>
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="28" t="s">
         <v>214</v>
       </c>
-      <c r="D19" s="35" t="s">
+      <c r="D19" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="26" t="s">
         <v>215</v>
       </c>
       <c r="F19" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="D14:D16"/>
     <mergeCell ref="B3:B7"/>
     <mergeCell ref="B8:B10"/>
     <mergeCell ref="B11:B17"/>
@@ -2982,6 +3012,11 @@
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="C6:C7"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="D14:D16"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4237,6 +4272,231 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E04278-B534-4A3B-A49C-9E9E2900B92A}">
+  <dimension ref="D3:H14"/>
+  <sheetFormatPr defaultRowHeight="17"/>
+  <cols>
+    <col min="5" max="5" width="13.1640625" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" customWidth="1"/>
+    <col min="7" max="7" width="9.58203125" customWidth="1"/>
+    <col min="8" max="8" width="13.58203125" customWidth="1"/>
+    <col min="9" max="9" width="11.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="4:8">
+      <c r="D3" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="4" spans="4:8">
+      <c r="D4" s="36" t="s">
+        <v>180</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="F4" s="41">
+        <v>10</v>
+      </c>
+      <c r="G4" s="42">
+        <v>0.1</v>
+      </c>
+      <c r="H4" s="41">
+        <f>F4/G4</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="4:8">
+      <c r="D5" s="36"/>
+      <c r="E5" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="F5" s="41">
+        <v>10</v>
+      </c>
+      <c r="G5" s="42">
+        <v>0.3</v>
+      </c>
+      <c r="H5" s="41">
+        <f t="shared" ref="H5:H14" si="0">F5/G5</f>
+        <v>33.333333333333336</v>
+      </c>
+    </row>
+    <row r="6" spans="4:8">
+      <c r="D6" s="36"/>
+      <c r="E6" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="F6" s="41">
+        <v>10</v>
+      </c>
+      <c r="G6" s="42">
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="41">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="4:8">
+      <c r="D7" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="F7" s="41">
+        <v>10</v>
+      </c>
+      <c r="G7" s="42">
+        <v>0.7</v>
+      </c>
+      <c r="H7" s="41">
+        <f t="shared" si="0"/>
+        <v>14.285714285714286</v>
+      </c>
+    </row>
+    <row r="8" spans="4:8">
+      <c r="D8" s="36"/>
+      <c r="E8" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="F8" s="41">
+        <v>10</v>
+      </c>
+      <c r="G8" s="42">
+        <v>0.8</v>
+      </c>
+      <c r="H8" s="41">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="9" spans="4:8">
+      <c r="D9" s="36"/>
+      <c r="E9" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="F9" s="41">
+        <v>10</v>
+      </c>
+      <c r="G9" s="42">
+        <v>1</v>
+      </c>
+      <c r="H9" s="41">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="4:8">
+      <c r="D10" s="36" t="s">
+        <v>194</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="F10" s="41">
+        <v>10</v>
+      </c>
+      <c r="G10" s="42">
+        <v>1</v>
+      </c>
+      <c r="H10" s="41">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="4:8">
+      <c r="D11" s="36"/>
+      <c r="E11" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="F11" s="41">
+        <v>10</v>
+      </c>
+      <c r="G11" s="42">
+        <v>1</v>
+      </c>
+      <c r="H11" s="41">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="4:8">
+      <c r="D12" s="36"/>
+      <c r="E12" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="F12" s="41">
+        <v>10</v>
+      </c>
+      <c r="G12" s="42">
+        <v>1</v>
+      </c>
+      <c r="H12" s="41">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="4:8">
+      <c r="D13" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="F13" s="41">
+        <v>10</v>
+      </c>
+      <c r="G13" s="42">
+        <v>1</v>
+      </c>
+      <c r="H13" s="41">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="4:8">
+      <c r="D14" s="36"/>
+      <c r="E14" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="F14" s="41">
+        <v>10</v>
+      </c>
+      <c r="G14" s="42">
+        <v>1</v>
+      </c>
+      <c r="H14" s="41">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="D13:D14"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3A88391-9A80-46CE-9830-8C683B3F75C7}">
   <dimension ref="A2:I46"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="17"/>
@@ -5461,7 +5721,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE83849-7D78-466C-B617-FE0D5CED810E}">
   <dimension ref="A2:I48"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="17"/>
@@ -6710,6 +6970,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="046fe32c-d480-456a-a3e2-649e42f9d10d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a09ad84a-4c15-4094-bc27-8774ad27384e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100670FC0B7DAAA2648AE207ABD5A3766C1" ma:contentTypeVersion="17" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="3190ee9720ce1ebb7a394bc4ca406abb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="046fe32c-d480-456a-a3e2-649e42f9d10d" xmlns:ns3="a09ad84a-4c15-4094-bc27-8774ad27384e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="90eebbbff0994ae2791f9232b9cc1961" ns2:_="" ns3:_="">
     <xsd:import namespace="046fe32c-d480-456a-a3e2-649e42f9d10d"/>
@@ -6956,27 +7236,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B192AAF-2CCD-4327-9FD3-147A8C4BEF5C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="046fe32c-d480-456a-a3e2-649e42f9d10d"/>
+    <ds:schemaRef ds:uri="a09ad84a-4c15-4094-bc27-8774ad27384e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="046fe32c-d480-456a-a3e2-649e42f9d10d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="a09ad84a-4c15-4094-bc27-8774ad27384e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{829F14DF-6A78-4A9E-804E-209273E51F9E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79B3285D-C571-4BE2-AA52-AFC1E49A7EE3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6993,23 +7272,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{829F14DF-6A78-4A9E-804E-209273E51F9E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B192AAF-2CCD-4327-9FD3-147A8C4BEF5C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="046fe32c-d480-456a-a3e2-649e42f9d10d"/>
-    <ds:schemaRef ds:uri="a09ad84a-4c15-4094-bc27-8774ad27384e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>